--- a/Assets/Data/Dungeon2012.xlsx
+++ b/Assets/Data/Dungeon2012.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -44,6 +44,9 @@
     <t>■</t>
   </si>
   <si>
+    <t>Out</t>
+  </si>
+  <si>
     <t>Un</t>
   </si>
 </sst>
@@ -52,9 +55,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -73,8 +76,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -88,15 +152,30 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -112,91 +191,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -207,6 +202,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,7 +229,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -238,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -256,25 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,13 +337,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,103 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,26 +420,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -451,30 +434,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,8 +456,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,6 +505,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -525,145 +528,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1056,10 +1059,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="B2">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1480,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>8</v>
@@ -1554,9 +1557,7 @@
       <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1629,9 +1630,7 @@
       <c r="H8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1701,9 +1700,13 @@
       <c r="G9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1772,7 +1775,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">

--- a/Assets/Data/Dungeon2012.xlsx
+++ b/Assets/Data/Dungeon2012.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -41,6 +41,9 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
     <t>■</t>
   </si>
   <si>
@@ -55,10 +58,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -76,40 +79,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,22 +116,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,14 +132,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -175,7 +170,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,14 +186,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -214,7 +217,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,6 +229,18 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -241,7 +256,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,31 +358,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,109 +400,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -403,13 +412,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,6 +423,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -456,24 +483,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -487,21 +496,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,6 +514,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -528,145 +531,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1206,7 +1209,9 @@
       <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -1281,7 +1286,9 @@
       <c r="P3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -1356,7 +1363,9 @@
       <c r="P4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1402,19 +1411,19 @@
         <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>8</v>
@@ -1431,7 +1440,9 @@
       <c r="P5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1477,19 +1488,19 @@
         <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>8</v>
@@ -1506,7 +1517,9 @@
       <c r="P6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1552,17 +1565,17 @@
         <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>8</v>
@@ -1579,7 +1592,9 @@
       <c r="P7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1625,17 +1640,17 @@
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>8</v>
@@ -1652,7 +1667,9 @@
       <c r="P8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1698,17 +1715,17 @@
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>8</v>
@@ -1725,7 +1742,9 @@
       <c r="P9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1771,15 +1790,15 @@
         <v>8</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>8</v>
@@ -1796,7 +1815,9 @@
       <c r="P10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1842,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>8</v>
@@ -1865,7 +1886,9 @@
       <c r="P11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1911,17 +1934,17 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>8</v>
@@ -1938,7 +1961,9 @@
       <c r="P12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1987,11 +2012,11 @@
         <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>8</v>
@@ -2011,7 +2036,9 @@
       <c r="P13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -2060,11 +2087,11 @@
         <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>8</v>
@@ -2084,7 +2111,9 @@
       <c r="P14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -2114,26 +2143,52 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -2163,28 +2218,54 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -2214,22 +2295,54 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
